--- a/Data/AllUpcomingEvents.xlsx
+++ b/Data/AllUpcomingEvents.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\briea\source\repos\group-project-part-2-behn\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9334473-80B7-4837-AF7D-1F05DA55EB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="84">
   <si>
     <t>Time</t>
   </si>
@@ -251,30 +260,39 @@
   </si>
   <si>
     <t>Toyota Center Houston, TX</t>
+  </si>
+  <si>
+    <t>Los Angeles Clippers</t>
+  </si>
+  <si>
+    <t>Capital One Arena, D.C</t>
+  </si>
+  <si>
+    <t>United Center, IL</t>
+  </si>
+  <si>
+    <t>Golden 1 Center, CA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
@@ -284,7 +302,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -300,27 +318,39 @@
     </fill>
   </fills>
   <borders count="4">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF8ED973"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF8ED973"/>
       </top>
       <bottom style="thin">
         <color rgb="FF8ED973"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF8ED973"/>
       </top>
       <bottom style="thin">
         <color rgb="FF8ED973"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF8ED973"/>
       </right>
@@ -330,93 +360,44 @@
       <bottom style="thin">
         <color rgb="FF8ED973"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -433,43 +414,67 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Sheet1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Sheet1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G60" displayName="Table1" name="Table1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:G75">
   <tableColumns count="7">
-    <tableColumn name="Time" id="1"/>
-    <tableColumn name="Team 1" id="2"/>
-    <tableColumn name="Team 2" id="3"/>
-    <tableColumn name="Where to Listen" id="4"/>
-    <tableColumn name="Arena" id="5"/>
-    <tableColumn name="Date" id="6"/>
-    <tableColumn name="Category" id="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Time"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Team 1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Team 2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Where to Listen"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Arena"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Date"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Category"/>
   </tableColumns>
-  <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Sheet1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -659,20 +664,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G75"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="22.63"/>
+    <col min="1" max="6" width="22.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:7" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -695,7 +703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:7" ht="22.5" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -708,40 +716,40 @@
       <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7">
-        <v>46105.0</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="F2" s="6">
+        <v>46105</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="11">
-        <v>46105.0</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
+      <c r="F3" s="10">
+        <v>46105</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="22.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -757,37 +765,37 @@
       <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="7">
-        <v>46105.0</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="F4" s="6">
+        <v>46105</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="11">
-        <v>46105.0</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
+      <c r="F5" s="10">
+        <v>46105</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="22.5" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -803,37 +811,37 @@
       <c r="E6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="7">
-        <v>46106.0</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="F6" s="6">
+        <v>46106</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="10" t="s">
+      <c r="D7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="11">
-        <v>46106.0</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
+      <c r="F7" s="10">
+        <v>46106</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="22.5" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -849,37 +857,37 @@
       <c r="E8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="7">
-        <v>46106.0</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="F8" s="6">
+        <v>46106</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="11">
-        <v>46106.0</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
+      <c r="F9" s="10">
+        <v>46106</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="22.5" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -895,37 +903,37 @@
       <c r="E10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="7">
-        <v>46106.0</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="F10" s="6">
+        <v>46106</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="11">
-        <v>46106.0</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
+      <c r="F11" s="10">
+        <v>46106</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="22.5" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
@@ -941,37 +949,37 @@
       <c r="E12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="7">
-        <v>46106.0</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="F12" s="6">
+        <v>46106</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="D13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="11">
-        <v>46106.0</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
+      <c r="F13" s="10">
+        <v>46106</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="22.5" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
@@ -987,37 +995,37 @@
       <c r="E14" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="7">
-        <v>46106.0</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="9" t="s">
+      <c r="F14" s="6">
+        <v>46106</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A15" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="11">
-        <v>46106.0</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
+      <c r="F15" s="10">
+        <v>46106</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="22.5" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>49</v>
       </c>
@@ -1033,37 +1041,37 @@
       <c r="E16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="7">
-        <v>46106.0</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="F16" s="6">
+        <v>46106</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="D17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="11">
-        <v>46106.0</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
+      <c r="F17" s="10">
+        <v>46106</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="22.5" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>7</v>
       </c>
@@ -1079,37 +1087,37 @@
       <c r="E18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="7">
-        <v>46107.0</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="F18" s="6">
+        <v>46107</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="D19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="11">
-        <v>46107.0</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
+      <c r="F19" s="10">
+        <v>46107</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="22.5" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>7</v>
       </c>
@@ -1125,37 +1133,37 @@
       <c r="E20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="7">
-        <v>46107.0</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="9" t="s">
+      <c r="F20" s="6">
+        <v>46107</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="D21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="11">
-        <v>46108.0</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
+      <c r="F21" s="10">
+        <v>46108</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="22.5" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
@@ -1171,37 +1179,37 @@
       <c r="E22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="7">
-        <v>46108.0</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="9" t="s">
+      <c r="F22" s="6">
+        <v>46108</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A23" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="10" t="s">
+      <c r="D23" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="11">
-        <v>46108.0</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" ht="22.5" customHeight="1">
+      <c r="F23" s="10">
+        <v>46108</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="22.5" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>17</v>
       </c>
@@ -1217,37 +1225,37 @@
       <c r="E24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="7">
-        <v>46108.0</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="9" t="s">
+      <c r="F24" s="6">
+        <v>46108</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="10" t="s">
+      <c r="D25" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="11">
-        <v>46108.0</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" ht="22.5" customHeight="1">
+      <c r="F25" s="10">
+        <v>46108</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="22.5" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>64</v>
       </c>
@@ -1263,37 +1271,37 @@
       <c r="E26" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F26" s="7">
-        <v>46108.0</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="9" t="s">
+      <c r="F26" s="6">
+        <v>46108</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A27" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="10" t="s">
+      <c r="D27" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F27" s="11">
-        <v>46108.0</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" ht="22.5" customHeight="1">
+      <c r="F27" s="10">
+        <v>46108</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="22.5" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>49</v>
       </c>
@@ -1309,37 +1317,37 @@
       <c r="E28" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="7">
-        <v>46108.0</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="9" t="s">
+      <c r="F28" s="6">
+        <v>46108</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A29" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="10" t="s">
+      <c r="D29" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="11">
-        <v>46108.0</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" ht="22.5" customHeight="1">
+      <c r="F29" s="10">
+        <v>46108</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="22.5" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>58</v>
       </c>
@@ -1355,37 +1363,37 @@
       <c r="E30" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="7">
-        <v>46108.0</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="9" t="s">
+      <c r="F30" s="6">
+        <v>46108</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A31" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="D31" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F31" s="11">
-        <v>46109.0</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
+      <c r="F31" s="10">
+        <v>46109</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="22.5" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>69</v>
       </c>
@@ -1401,37 +1409,37 @@
       <c r="E32" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="7">
-        <v>46109.0</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="9" t="s">
+      <c r="F32" s="6">
+        <v>46109</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A33" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="D33" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F33" s="11">
-        <v>46109.0</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" ht="22.5" customHeight="1">
+      <c r="F33" s="10">
+        <v>46109</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="22.5" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>13</v>
       </c>
@@ -1447,37 +1455,37 @@
       <c r="E34" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="7">
-        <v>46109.0</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="9" t="s">
+      <c r="F34" s="6">
+        <v>46109</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A35" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="10" t="s">
+      <c r="D35" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F35" s="11">
-        <v>46109.0</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
+      <c r="F35" s="10">
+        <v>46109</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="22.5" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>49</v>
       </c>
@@ -1493,37 +1501,37 @@
       <c r="E36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="7">
-        <v>46109.0</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="9" t="s">
+      <c r="F36" s="6">
+        <v>46109</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A37" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="10" t="s">
+      <c r="D37" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F37" s="11">
-        <v>46110.0</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
+      <c r="F37" s="10">
+        <v>46110</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="22.5" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>73</v>
       </c>
@@ -1539,37 +1547,37 @@
       <c r="E38" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="7">
-        <v>46110.0</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="9" t="s">
+      <c r="F38" s="6">
+        <v>46110</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A39" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="10" t="s">
+      <c r="D39" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F39" s="11">
-        <v>46110.0</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
+      <c r="F39" s="10">
+        <v>46110</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="22.5" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>70</v>
       </c>
@@ -1585,37 +1593,37 @@
       <c r="E40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="7">
-        <v>46110.0</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="9" t="s">
+      <c r="F40" s="6">
+        <v>46110</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A41" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D41" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="10" t="s">
+      <c r="D41" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F41" s="11">
-        <v>46110.0</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" ht="22.5" customHeight="1">
+      <c r="F41" s="10">
+        <v>46110</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="22.5" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>70</v>
       </c>
@@ -1631,37 +1639,37 @@
       <c r="E42" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F42" s="7">
-        <v>46110.0</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="9" t="s">
+      <c r="F42" s="6">
+        <v>46110</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A43" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="10" t="s">
+      <c r="D43" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="11">
-        <v>46110.0</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
+      <c r="F43" s="10">
+        <v>46110</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="22.5" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>13</v>
       </c>
@@ -1677,37 +1685,37 @@
       <c r="E44" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F44" s="7">
-        <v>46110.0</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="9" t="s">
+      <c r="F44" s="6">
+        <v>46110</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A45" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="10" t="s">
+      <c r="D45" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F45" s="11">
-        <v>46110.0</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" ht="22.5" customHeight="1">
+      <c r="F45" s="10">
+        <v>46110</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="22.5" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>7</v>
       </c>
@@ -1723,37 +1731,37 @@
       <c r="E46" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F46" s="7">
-        <v>46111.0</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="9" t="s">
+      <c r="F46" s="6">
+        <v>46111</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A47" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D47" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="10" t="s">
+      <c r="D47" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F47" s="11">
-        <v>46111.0</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
+      <c r="F47" s="10">
+        <v>46111</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="22.5" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>17</v>
       </c>
@@ -1769,37 +1777,37 @@
       <c r="E48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F48" s="7">
-        <v>46111.0</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="9" t="s">
+      <c r="F48" s="6">
+        <v>46111</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A49" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D49" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="10" t="s">
+      <c r="D49" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F49" s="11">
-        <v>46111.0</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
+      <c r="F49" s="10">
+        <v>46111</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="22.5" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>64</v>
       </c>
@@ -1815,37 +1823,37 @@
       <c r="E50" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F50" s="7">
-        <v>46111.0</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="9" t="s">
+      <c r="F50" s="6">
+        <v>46111</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A51" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="10" t="s">
+      <c r="D51" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F51" s="11">
-        <v>46111.0</v>
-      </c>
-      <c r="G51" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" ht="22.5" customHeight="1">
+      <c r="F51" s="10">
+        <v>46111</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="22.5" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>45</v>
       </c>
@@ -1861,37 +1869,37 @@
       <c r="E52" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="7">
-        <v>46111.0</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="9" t="s">
+      <c r="F52" s="6">
+        <v>46111</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A53" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="10" t="s">
+      <c r="D53" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F53" s="11">
-        <v>46111.0</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" ht="22.5" customHeight="1">
+      <c r="F53" s="10">
+        <v>46111</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="22.5" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>7</v>
       </c>
@@ -1907,37 +1915,37 @@
       <c r="E54" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F54" s="7">
-        <v>46112.0</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="9" t="s">
+      <c r="F54" s="6">
+        <v>46112</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A55" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="10" t="s">
+      <c r="D55" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F55" s="11">
-        <v>46112.0</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" ht="22.5" customHeight="1">
+      <c r="F55" s="10">
+        <v>46112</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="22.5" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>17</v>
       </c>
@@ -1953,37 +1961,37 @@
       <c r="E56" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F56" s="7">
-        <v>46112.0</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="9" t="s">
+      <c r="F56" s="6">
+        <v>46112</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A57" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="10" t="s">
+      <c r="D57" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F57" s="11">
-        <v>46112.0</v>
-      </c>
-      <c r="G57" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" ht="22.5" customHeight="1">
+      <c r="F57" s="10">
+        <v>46112</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="22.5" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>17</v>
       </c>
@@ -1999,37 +2007,37 @@
       <c r="E58" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F58" s="7">
-        <v>46112.0</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="9" t="s">
+      <c r="F58" s="6">
+        <v>46112</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A59" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D59" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="10" t="s">
+      <c r="D59" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F59" s="11">
-        <v>46112.0</v>
-      </c>
-      <c r="G59" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" customHeight="1">
+      <c r="F59" s="10">
+        <v>46112</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="22.5" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>21</v>
       </c>
@@ -2045,17 +2053,362 @@
       <c r="E60" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F60" s="7">
-        <v>46112.0</v>
-      </c>
-      <c r="G60" s="8" t="s">
+      <c r="F60" s="6">
+        <v>46112</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A61" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A62" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" t="s">
+        <v>55</v>
+      </c>
+      <c r="C64" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" t="s">
+        <v>79</v>
+      </c>
+      <c r="F64" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A65" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>82</v>
+      </c>
+      <c r="F65" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A66" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A67" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" t="s">
+        <v>83</v>
+      </c>
+      <c r="F67" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A68" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F68" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A69" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F69" s="13">
+        <v>46113</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A70" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="13">
+        <v>46114</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A71" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F71" s="13">
+        <v>46114</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A72" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F72" s="13">
+        <v>46114</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A73" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F73" s="13">
+        <v>46114</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A74" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B74" t="s">
+        <v>53</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F74" s="13">
+        <v>46114</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A75" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C75" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F75" s="13">
+        <v>46114</v>
+      </c>
+      <c r="G75" s="12" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>